--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N204_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N204_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.367871096468376</v>
+        <v>0.709779053176111</v>
       </c>
       <c r="D2" t="n">
-        <v>35.04322508337924</v>
+        <v>5.694524076049126</v>
       </c>
       <c r="E2" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F2" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.71284993566308</v>
+        <v>6.615838114545251</v>
       </c>
       <c r="D3" t="n">
-        <v>14.22691917806728</v>
+        <v>2.311874366435933</v>
       </c>
       <c r="E3" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F3" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.00396313587421</v>
+        <v>7.80064400957956</v>
       </c>
       <c r="D4" t="n">
-        <v>20.29718540429759</v>
+        <v>3.298292628198359</v>
       </c>
       <c r="E4" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F4" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.20748291459476</v>
+        <v>6.858715973621648</v>
       </c>
       <c r="D5" t="n">
-        <v>17.58657365327901</v>
+        <v>2.857818218657839</v>
       </c>
       <c r="E5" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F5" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.2211374282921</v>
+        <v>6.210934832097467</v>
       </c>
       <c r="D6" t="n">
-        <v>40.80351650661207</v>
+        <v>6.630571432324461</v>
       </c>
       <c r="E6" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F6" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.52932224598789</v>
+        <v>4.473514864973032</v>
       </c>
       <c r="D7" t="n">
-        <v>42.29464332233687</v>
+        <v>6.872879539879741</v>
       </c>
       <c r="E7" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F7" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.00657780874821</v>
+        <v>3.088568893921584</v>
       </c>
       <c r="D8" t="n">
-        <v>34.7922405142296</v>
+        <v>5.653739083562311</v>
       </c>
       <c r="E8" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F8" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.09133306290472</v>
+        <v>6.514841622722017</v>
       </c>
       <c r="D9" t="n">
-        <v>14.61630232764702</v>
+        <v>2.37514912824264</v>
       </c>
       <c r="E9" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F9" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.88238017426859</v>
+        <v>2.580886778318646</v>
       </c>
       <c r="D10" t="n">
-        <v>29.20616373302047</v>
+        <v>4.746001606615826</v>
       </c>
       <c r="E10" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F10" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>8.860022573334675</v>
+        <v>1.439753668166885</v>
       </c>
       <c r="D11" t="n">
-        <v>21.91460700081113</v>
+        <v>3.561123637631809</v>
       </c>
       <c r="E11" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F11" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.27331636276289</v>
+        <v>1.994413908948971</v>
       </c>
       <c r="D12" t="n">
-        <v>33.67817283427446</v>
+        <v>5.4727030855696</v>
       </c>
       <c r="E12" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F12" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.04605884431778</v>
+        <v>3.74498456220164</v>
       </c>
       <c r="D13" t="n">
-        <v>26.26002458407513</v>
+        <v>4.267253994912209</v>
       </c>
       <c r="E13" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F13" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.76895048885076</v>
+        <v>4.999954454438248</v>
       </c>
       <c r="D14" t="n">
-        <v>21.2350860492133</v>
+        <v>3.450701482997161</v>
       </c>
       <c r="E14" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F14" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>20.43532014998878</v>
+        <v>3.320739524373177</v>
       </c>
       <c r="D15" t="n">
-        <v>21.22436859419432</v>
+        <v>3.448959896556578</v>
       </c>
       <c r="E15" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F15" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>10.70973099336012</v>
+        <v>1.74033128642102</v>
       </c>
       <c r="D16" t="n">
-        <v>18.01555665628466</v>
+        <v>2.927527956646258</v>
       </c>
       <c r="E16" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F16" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>26.03790464173566</v>
+        <v>4.231159504282044</v>
       </c>
       <c r="D17" t="n">
-        <v>11.45966065039547</v>
+        <v>1.862194855689263</v>
       </c>
       <c r="E17" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F17" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>26.47349063442884</v>
+        <v>4.301942228094687</v>
       </c>
       <c r="D18" t="n">
-        <v>19.17909031071123</v>
+        <v>3.116602175490576</v>
       </c>
       <c r="E18" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F18" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>56.04382505017152</v>
+        <v>9.107121570652872</v>
       </c>
       <c r="D19" t="n">
-        <v>34.36608470247634</v>
+        <v>5.584488764152405</v>
       </c>
       <c r="E19" t="n">
-        <v>14.1137002383005</v>
+        <v>2.293476288723831</v>
       </c>
       <c r="F19" t="n">
-        <v>9.221654351557033</v>
+        <v>1.498518832128018</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
